--- a/data/age.xlsx
+++ b/data/age.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0647F498-B306-4FFE-8644-7BE2BE60DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{0647F498-B306-4FFE-8644-7BE2BE60DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB84C58-6FA1-480B-8297-24A07B014B16}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1335" windowWidth="20805" windowHeight="14865" xr2:uid="{4573E8DE-863E-4F9D-A883-6066420650A6}"/>
+    <workbookView xWindow="10050" yWindow="1710" windowWidth="4920" windowHeight="14685" xr2:uid="{4573E8DE-863E-4F9D-A883-6066420650A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="424">
   <si>
     <t>象主（ズニーシャ）</t>
   </si>
@@ -87,9 +87,6 @@
     <t>黒炭せみ丸（享年）</t>
   </si>
   <si>
-    <t>83（20年前）</t>
-  </si>
-  <si>
     <t>クローバー博士（享年）</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
     <t>霜月コウ三郎（享年）</t>
   </si>
   <si>
-    <t>68（13年前）</t>
-  </si>
-  <si>
     <t>ハイルディン</t>
   </si>
   <si>
@@ -330,9 +324,6 @@
     <t>ベン・ベックマン</t>
   </si>
   <si>
-    <t>ミス・メリークリスマス</t>
-  </si>
-  <si>
     <t>コブラ</t>
   </si>
   <si>
@@ -345,9 +336,6 @@
     <t>霜月牛マル（享年）</t>
   </si>
   <si>
-    <t>50（20年前）</t>
-  </si>
-  <si>
     <t>トレーボル</t>
   </si>
   <si>
@@ -423,9 +411,6 @@
     <t>雨月天ぷら（享年）</t>
   </si>
   <si>
-    <t>45（20年前）</t>
-  </si>
-  <si>
     <t>マルコ</t>
   </si>
   <si>
@@ -462,9 +447,6 @@
     <t>風月おむすび（享年）</t>
   </si>
   <si>
-    <t>44（20年前）</t>
-  </si>
-  <si>
     <t>茶ひげ</t>
   </si>
   <si>
@@ -651,9 +633,6 @@
     <t>シンドリー（享年）</t>
   </si>
   <si>
-    <t>24（12年前）</t>
-  </si>
-  <si>
     <t>ミョスガルド聖</t>
   </si>
   <si>
@@ -786,9 +765,6 @@
     <t>イナズマ</t>
   </si>
   <si>
-    <t>Mr.4</t>
-  </si>
-  <si>
     <t>サンダーソニア</t>
   </si>
   <si>
@@ -846,9 +822,6 @@
     <t>ペンギン</t>
   </si>
   <si>
-    <t>ミス・ダブルフィンガー</t>
-  </si>
-  <si>
     <t>コリブー</t>
   </si>
   <si>
@@ -1267,20 +1240,12 @@
   </si>
   <si>
     <t>ペッツ</t>
-  </si>
-  <si>
-    <t>85（20年前）</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ジニー（享年）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>39（12年前）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アナナ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1350,6 +1315,18 @@
   </si>
   <si>
     <t>ヒルルク（享年）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベーブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロフィー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ザラ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1722,1439 +1699,1439 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="B1">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="B2">
-        <v>159</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>399</v>
       </c>
       <c r="B3">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>396</v>
       </c>
       <c r="B4">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>397</v>
       </c>
       <c r="B5">
-        <v>408</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>398</v>
       </c>
       <c r="B6">
-        <v>344</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>403</v>
       </c>
       <c r="B7">
-        <v>160</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>395</v>
       </c>
       <c r="B8">
-        <v>160</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>394</v>
       </c>
       <c r="B9">
-        <v>160</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="B10">
-        <v>156</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="B11">
-        <v>153</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B12">
         <v>11</v>
-      </c>
-      <c r="B12">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>392</v>
       </c>
       <c r="B13">
-        <v>141</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>393</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>389</v>
       </c>
       <c r="B15">
-        <v>105</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>411</v>
+        <v>383</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
+        <v>384</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>385</v>
       </c>
       <c r="B18">
-        <v>85</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="B20">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="B21">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>380</v>
       </c>
       <c r="B22">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>405</v>
       </c>
       <c r="B23">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>25</v>
+        <v>381</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>382</v>
       </c>
       <c r="B25">
-        <v>81</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>372</v>
       </c>
       <c r="B26">
-        <v>81</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>373</v>
       </c>
       <c r="B27">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>374</v>
       </c>
       <c r="B28">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>404</v>
       </c>
       <c r="B29">
-        <v>78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>375</v>
       </c>
       <c r="B30">
-        <v>78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>376</v>
       </c>
       <c r="B31">
-        <v>78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>377</v>
       </c>
       <c r="B32">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="B33">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>379</v>
       </c>
       <c r="B34">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>368</v>
       </c>
       <c r="B35">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>369</v>
       </c>
       <c r="B36">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="B37">
-        <v>75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>371</v>
       </c>
       <c r="B38">
-        <v>75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="B39">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>363</v>
       </c>
       <c r="B40">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="B41">
-        <v>72</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>406</v>
       </c>
       <c r="B42">
-        <v>73</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="B43">
-        <v>72</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>366</v>
       </c>
       <c r="B44">
-        <v>72</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>367</v>
       </c>
       <c r="B45">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>359</v>
       </c>
       <c r="B46">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>360</v>
       </c>
       <c r="B47">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>361</v>
       </c>
       <c r="B48">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>344</v>
       </c>
       <c r="B49">
-        <v>69</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>353</v>
       </c>
       <c r="B50">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>354</v>
       </c>
       <c r="B51">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>355</v>
       </c>
       <c r="B52">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>356</v>
       </c>
       <c r="B53">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>357</v>
       </c>
       <c r="B54">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>358</v>
       </c>
       <c r="B55">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>345</v>
       </c>
       <c r="B56">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="B57">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="B58">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>348</v>
       </c>
       <c r="B59">
-        <v>64</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="B60">
-        <v>61</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>350</v>
       </c>
       <c r="B61">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>351</v>
       </c>
       <c r="B62">
-        <v>61</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>352</v>
       </c>
       <c r="B63">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>332</v>
       </c>
       <c r="B64">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>333</v>
       </c>
       <c r="B65">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>334</v>
       </c>
       <c r="B66">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>335</v>
       </c>
       <c r="B67">
-        <v>81</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>336</v>
       </c>
       <c r="B68">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>337</v>
       </c>
       <c r="B69">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>338</v>
       </c>
       <c r="B70">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>339</v>
       </c>
       <c r="B71">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>340</v>
       </c>
       <c r="B72">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>341</v>
       </c>
       <c r="B73">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="B74">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="B75">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="B76">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="B77">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="B78">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="B79">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="B80">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="B81">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="B82">
-        <v>54</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="B83">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="B84">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="B85">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>311</v>
       </c>
       <c r="B86">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>312</v>
       </c>
       <c r="B87">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>313</v>
       </c>
       <c r="B88">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>314</v>
       </c>
       <c r="B89">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>315</v>
       </c>
       <c r="B90">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="B91">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>317</v>
       </c>
       <c r="B92">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>318</v>
       </c>
       <c r="B93">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>319</v>
       </c>
       <c r="B94">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B95">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>321</v>
       </c>
       <c r="B96">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>412</v>
-      </c>
-      <c r="B97" t="s">
-        <v>413</v>
+        <v>322</v>
+      </c>
+      <c r="B97">
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="B98">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="B99">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>430</v>
+        <v>210</v>
       </c>
       <c r="B100">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="B101">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="B102">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
       <c r="B103">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>102</v>
-      </c>
-      <c r="B104" t="s">
-        <v>103</v>
+        <v>299</v>
+      </c>
+      <c r="B104">
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="B105">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>301</v>
       </c>
       <c r="B106">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>106</v>
+        <v>302</v>
       </c>
       <c r="B107">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>304</v>
       </c>
       <c r="B108">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>305</v>
       </c>
       <c r="B109">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>429</v>
+        <v>306</v>
       </c>
       <c r="B110">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="B111">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>309</v>
       </c>
       <c r="B112">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="B113">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="B114">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>278</v>
       </c>
       <c r="B115">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>280</v>
       </c>
       <c r="B116">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="B117">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>409</v>
       </c>
       <c r="B118">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="B119">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="B120">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="B121">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>428</v>
+        <v>295</v>
       </c>
       <c r="B122">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>407</v>
       </c>
       <c r="B123">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="B124">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="B125">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="B126">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="B127">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="B128">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>427</v>
+        <v>271</v>
       </c>
       <c r="B129">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="B130">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
       <c r="B131">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>128</v>
-      </c>
-      <c r="B132" t="s">
-        <v>129</v>
+        <v>281</v>
+      </c>
+      <c r="B132">
+        <v>27</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="B133">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>426</v>
+        <v>283</v>
       </c>
       <c r="B134">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>284</v>
       </c>
       <c r="B135">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>132</v>
+        <v>285</v>
       </c>
       <c r="B136">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>133</v>
+        <v>286</v>
       </c>
       <c r="B137">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>290</v>
       </c>
       <c r="B138">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="B139">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="B140">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="B141">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="B142">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="B143">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="B144">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>141</v>
-      </c>
-      <c r="B145" t="s">
-        <v>142</v>
+        <v>423</v>
+      </c>
+      <c r="B145">
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="B146">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>144</v>
+        <v>273</v>
       </c>
       <c r="B147">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>145</v>
+        <v>274</v>
       </c>
       <c r="B148">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="B149">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>147</v>
+        <v>277</v>
       </c>
       <c r="B150">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="B151">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="B152">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="B153">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="B154">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="B155">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="B156">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="B157">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="B158">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="B159">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="B160">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="B161">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>159</v>
+        <v>408</v>
       </c>
       <c r="B162">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="B163">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="B164">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="B165">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B166">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="B167">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="B168">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="B169">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="B170">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>168</v>
+        <v>421</v>
       </c>
       <c r="B171">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B172">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="B173">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="B174">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>247</v>
       </c>
       <c r="B175">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>173</v>
+        <v>248</v>
       </c>
       <c r="B176">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="B177">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="B178">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="B179">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="B180">
         <v>30</v>
@@ -3162,239 +3139,239 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="B181">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="B182">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="B183">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="B184">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="B185">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>183</v>
+        <v>410</v>
       </c>
       <c r="B186">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="B187">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B188">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="B189">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="B190">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="B191">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="B192">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="B193">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="B194">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="B195">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="B196">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B197">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="B198">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="B199">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="B200">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="B201">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="B202">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="B203">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B204">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B205">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B206">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B207">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B208">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>204</v>
-      </c>
-      <c r="B209" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+      <c r="B209">
+        <v>34</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B210">
         <v>35</v>
@@ -3402,7 +3379,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B211">
         <v>35</v>
@@ -3410,7 +3387,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B212">
         <v>35</v>
@@ -3418,7 +3395,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B213">
         <v>35</v>
@@ -3426,7 +3403,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B214">
         <v>35</v>
@@ -3434,7 +3411,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B215">
         <v>35</v>
@@ -3442,7 +3419,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B216">
         <v>35</v>
@@ -3450,7 +3427,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B217">
         <v>35</v>
@@ -3458,7 +3435,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B218">
         <v>35</v>
@@ -3466,7 +3443,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B219">
         <v>35</v>
@@ -3474,7 +3451,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B220">
         <v>35</v>
@@ -3482,1637 +3459,1640 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="B221">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="B222">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="B223">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="B224">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="B225">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="B226">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="B227">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="B228">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B229">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B230">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="B231">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="B232">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>229</v>
+        <v>413</v>
       </c>
       <c r="B233">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="B234">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="B235">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="B236">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="B237">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="B238">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="B239">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>414</v>
       </c>
       <c r="B240">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="B241">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>423</v>
+        <v>182</v>
       </c>
       <c r="B242">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="B243">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>421</v>
+        <v>184</v>
       </c>
       <c r="B244">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>238</v>
+        <v>2</v>
       </c>
       <c r="B245">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>239</v>
+        <v>3</v>
       </c>
       <c r="B246">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="B247">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="B248">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="B249">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="B250">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="B251">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>245</v>
+        <v>402</v>
       </c>
       <c r="B252">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="B253">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="B254">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="B255">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="B256">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="B257">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>251</v>
+        <v>168</v>
       </c>
       <c r="B258">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="B259">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="B260">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="B261">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
       <c r="B262">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="B263">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>257</v>
+        <v>157</v>
       </c>
       <c r="B264">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="B265">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="B266">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="B267">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>261</v>
+        <v>161</v>
       </c>
       <c r="B268">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>262</v>
+        <v>143</v>
       </c>
       <c r="B269">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="B270">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="B271">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B272">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="B273">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="B274">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
       <c r="B275">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="B276">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="B277">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="B278">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>419</v>
+        <v>138</v>
       </c>
       <c r="B279">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="B280">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>273</v>
+        <v>146</v>
       </c>
       <c r="B281">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>274</v>
+        <v>132</v>
       </c>
       <c r="B282">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="B283">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="B284">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="B285">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="B286">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="B287">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="B288">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>281</v>
+        <v>415</v>
       </c>
       <c r="B289">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>282</v>
+        <v>126</v>
       </c>
       <c r="B290">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="B291">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>284</v>
+        <v>129</v>
       </c>
       <c r="B292">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="B293">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>286</v>
+        <v>131</v>
       </c>
       <c r="B294">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="B295">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>288</v>
+        <v>137</v>
       </c>
       <c r="B296">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>289</v>
+        <v>139</v>
       </c>
       <c r="B297">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="B298">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>291</v>
+        <v>124</v>
       </c>
       <c r="B299">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="B300">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>293</v>
+        <v>114</v>
       </c>
       <c r="B301">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="B302">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>295</v>
+        <v>119</v>
       </c>
       <c r="B303">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>296</v>
+        <v>120</v>
       </c>
       <c r="B304">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>420</v>
+        <v>121</v>
       </c>
       <c r="B305">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>297</v>
+        <v>416</v>
       </c>
       <c r="B306">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>298</v>
+        <v>122</v>
       </c>
       <c r="B307">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>299</v>
+        <v>103</v>
       </c>
       <c r="B308">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>300</v>
+        <v>109</v>
       </c>
       <c r="B309">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>301</v>
+        <v>110</v>
       </c>
       <c r="B310">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="B311">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="B312">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>304</v>
+        <v>113</v>
       </c>
       <c r="B313">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>305</v>
+        <v>417</v>
       </c>
       <c r="B314">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>418</v>
+        <v>116</v>
       </c>
       <c r="B315">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>306</v>
+        <v>117</v>
       </c>
       <c r="B316">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>307</v>
+        <v>118</v>
       </c>
       <c r="B317">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>308</v>
+        <v>67</v>
       </c>
       <c r="B318">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="B319">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>310</v>
+        <v>418</v>
       </c>
       <c r="B320">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>311</v>
+        <v>105</v>
       </c>
       <c r="B321">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>312</v>
+        <v>106</v>
       </c>
       <c r="B322">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="B323">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>314</v>
+        <v>97</v>
       </c>
       <c r="B324">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>315</v>
+        <v>100</v>
       </c>
       <c r="B325">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>316</v>
+        <v>104</v>
       </c>
       <c r="B326">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
-        <v>317</v>
+        <v>95</v>
       </c>
       <c r="B327">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>318</v>
+        <v>419</v>
       </c>
       <c r="B328">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>319</v>
+        <v>96</v>
       </c>
       <c r="B329">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
-        <v>320</v>
+        <v>98</v>
       </c>
       <c r="B330">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>321</v>
+        <v>101</v>
       </c>
       <c r="B331">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="B332">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>323</v>
+        <v>93</v>
       </c>
       <c r="B333">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>324</v>
+        <v>94</v>
       </c>
       <c r="B334">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="B335">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="B336">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>327</v>
+        <v>92</v>
       </c>
       <c r="B337">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>328</v>
+        <v>31</v>
       </c>
       <c r="B338">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="B339">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>330</v>
+        <v>86</v>
       </c>
       <c r="B340">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>331</v>
+        <v>87</v>
       </c>
       <c r="B341">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>332</v>
+        <v>88</v>
       </c>
       <c r="B342">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="B343">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="B344">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="B345">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="B346">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
-        <v>337</v>
+        <v>89</v>
       </c>
       <c r="B347">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
-        <v>338</v>
+        <v>72</v>
       </c>
       <c r="B348">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>339</v>
+        <v>73</v>
       </c>
       <c r="B349">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>340</v>
+        <v>76</v>
       </c>
       <c r="B350">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="B351">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="B352">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="B353">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
-        <v>344</v>
+        <v>166</v>
       </c>
       <c r="B354">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>345</v>
+        <v>69</v>
       </c>
       <c r="B355">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
-        <v>346</v>
+        <v>71</v>
       </c>
       <c r="B356">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>347</v>
+        <v>74</v>
       </c>
       <c r="B357">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
-        <v>348</v>
+        <v>75</v>
       </c>
       <c r="B358">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>349</v>
+        <v>70</v>
       </c>
       <c r="B359">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>350</v>
+        <v>66</v>
       </c>
       <c r="B360">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>351</v>
+        <v>64</v>
       </c>
       <c r="B361">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
-        <v>352</v>
+        <v>61</v>
       </c>
       <c r="B362">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>353</v>
+        <v>58</v>
       </c>
       <c r="B363">
-        <v>20</v>
+        <v>61</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="B364">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>355</v>
+        <v>62</v>
       </c>
       <c r="B365">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
-        <v>356</v>
+        <v>63</v>
       </c>
       <c r="B366">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>357</v>
+        <v>54</v>
       </c>
       <c r="B367">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
-        <v>358</v>
+        <v>55</v>
       </c>
       <c r="B368">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>359</v>
+        <v>56</v>
       </c>
       <c r="B369">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
-        <v>360</v>
+        <v>59</v>
       </c>
       <c r="B370">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>361</v>
+        <v>57</v>
       </c>
       <c r="B371">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>362</v>
+        <v>52</v>
       </c>
       <c r="B372">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>363</v>
+        <v>53</v>
       </c>
       <c r="B373">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>364</v>
+        <v>51</v>
       </c>
       <c r="B374">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>365</v>
+        <v>32</v>
       </c>
       <c r="B375">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="B376">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="B377">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>368</v>
+        <v>48</v>
       </c>
       <c r="B378">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
-        <v>369</v>
+        <v>49</v>
       </c>
       <c r="B379">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>370</v>
+        <v>23</v>
       </c>
       <c r="B380">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
-        <v>371</v>
+        <v>47</v>
       </c>
       <c r="B381">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
-        <v>372</v>
+        <v>44</v>
       </c>
       <c r="B382">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
-        <v>373</v>
+        <v>45</v>
       </c>
       <c r="B383">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
-        <v>417</v>
+        <v>46</v>
       </c>
       <c r="B384">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>374</v>
+        <v>43</v>
       </c>
       <c r="B385">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
-        <v>375</v>
+        <v>39</v>
       </c>
       <c r="B386">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
-        <v>376</v>
+        <v>41</v>
       </c>
       <c r="B387">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>377</v>
+        <v>42</v>
       </c>
       <c r="B388">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
-        <v>378</v>
+        <v>40</v>
       </c>
       <c r="B389">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>379</v>
+        <v>38</v>
       </c>
       <c r="B390">
-        <v>17</v>
+        <v>74</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="B391">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="B392">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
-        <v>382</v>
+        <v>33</v>
       </c>
       <c r="B393">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
-        <v>383</v>
+        <v>34</v>
       </c>
       <c r="B394">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
-        <v>415</v>
+        <v>35</v>
       </c>
       <c r="B395">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
-        <v>384</v>
+        <v>28</v>
       </c>
       <c r="B396">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="B397">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="B398">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
-        <v>387</v>
+        <v>26</v>
       </c>
       <c r="B399">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
-        <v>388</v>
+        <v>27</v>
       </c>
       <c r="B400">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>389</v>
+        <v>11</v>
       </c>
       <c r="B401">
-        <v>15</v>
+        <v>80</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
-        <v>416</v>
+        <v>24</v>
       </c>
       <c r="B402">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
-        <v>390</v>
+        <v>25</v>
       </c>
       <c r="B403">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
-        <v>391</v>
+        <v>65</v>
       </c>
       <c r="B404">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
-        <v>392</v>
+        <v>16</v>
       </c>
       <c r="B405">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="B406">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>394</v>
+        <v>15</v>
       </c>
       <c r="B407">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="B408">
-        <v>14</v>
+        <v>88</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="B409">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="B410">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="B411">
-        <v>13</v>
+        <v>97</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
-        <v>399</v>
+        <v>18</v>
       </c>
       <c r="B412">
-        <v>11</v>
+        <v>99</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
-        <v>400</v>
+        <v>14</v>
       </c>
       <c r="B413">
-        <v>11</v>
+        <v>105</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
-        <v>401</v>
+        <v>13</v>
       </c>
       <c r="B414">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="B415">
-        <v>11</v>
+        <v>141</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
-        <v>403</v>
+        <v>10</v>
       </c>
       <c r="B416">
-        <v>10</v>
+        <v>153</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
-        <v>404</v>
+        <v>9</v>
       </c>
       <c r="B417">
-        <v>9</v>
+        <v>156</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
-        <v>405</v>
+        <v>1</v>
       </c>
       <c r="B418">
-        <v>8</v>
+        <v>159</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
-        <v>406</v>
+        <v>6</v>
       </c>
       <c r="B419">
-        <v>8</v>
+        <v>160</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
-        <v>407</v>
+        <v>7</v>
       </c>
       <c r="B420">
-        <v>8</v>
+        <v>160</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
-        <v>414</v>
+        <v>8</v>
       </c>
       <c r="B421">
-        <v>8</v>
+        <v>160</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
-        <v>408</v>
+        <v>5</v>
       </c>
       <c r="B422">
-        <v>6</v>
+        <v>344</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
-        <v>409</v>
+        <v>4</v>
       </c>
       <c r="B423">
-        <v>4</v>
+        <v>408</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="B424">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B424">
+    <sortCondition ref="B401:B424"/>
+  </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/age.xlsx
+++ b/data/age.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{0647F498-B306-4FFE-8644-7BE2BE60DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB84C58-6FA1-480B-8297-24A07B014B16}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{0647F498-B306-4FFE-8644-7BE2BE60DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4537C760-3825-4B25-830A-3C441531E042}"/>
   <bookViews>
-    <workbookView xWindow="10050" yWindow="1710" windowWidth="4920" windowHeight="14685" xr2:uid="{4573E8DE-863E-4F9D-A883-6066420650A6}"/>
+    <workbookView xWindow="10515" yWindow="1080" windowWidth="13635" windowHeight="13170" xr2:uid="{4573E8DE-863E-4F9D-A883-6066420650A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,26 +34,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="424">
-  <si>
-    <t>象主（ズニーシャ）</t>
-  </si>
-  <si>
-    <t>オーズ(享年）</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="432">
   <si>
     <t>カルガラ</t>
   </si>
   <si>
-    <t>ノーランド</t>
-  </si>
-  <si>
     <t>ヤルル</t>
   </si>
   <si>
-    <t>ヨルル（享年）</t>
-  </si>
-  <si>
     <t>モーリー</t>
   </si>
   <si>
@@ -72,24 +60,9 @@
     <t>カルメル</t>
   </si>
   <si>
-    <t>くれは</t>
-  </si>
-  <si>
     <t>スルメ</t>
   </si>
   <si>
-    <t>サウロ（22年前）</t>
-  </si>
-  <si>
-    <t>黒炭ひぐらし（享年）</t>
-  </si>
-  <si>
-    <t>黒炭せみ丸（享年）</t>
-  </si>
-  <si>
-    <t>クローバー博士（享年）</t>
-  </si>
-  <si>
     <t>サンファン・ウルフ</t>
   </si>
   <si>
@@ -102,12 +75,6 @@
     <t>ブルック</t>
   </si>
   <si>
-    <t>ばばあ</t>
-  </si>
-  <si>
-    <t>霜月コウ三郎（享年）</t>
-  </si>
-  <si>
     <t>ハイルディン</t>
   </si>
   <si>
@@ -120,27 +87,12 @@
     <t>アマゾン</t>
   </si>
   <si>
-    <t>ガープ</t>
-  </si>
-  <si>
-    <t>レイリー</t>
-  </si>
-  <si>
     <t>チンジャオ</t>
   </si>
   <si>
-    <t>ロジャー（享年）</t>
-  </si>
-  <si>
-    <t>トム（享年）</t>
-  </si>
-  <si>
     <t>コニー</t>
   </si>
   <si>
-    <t>おつる</t>
-  </si>
-  <si>
     <t>バッキン</t>
   </si>
   <si>
@@ -150,12 +102,6 @@
     <t>ブードル</t>
   </si>
   <si>
-    <t>ゼファー</t>
-  </si>
-  <si>
-    <t>白ひげ（享年）</t>
-  </si>
-  <si>
     <t>クロッカス</t>
   </si>
   <si>
@@ -165,9 +111,6 @@
     <t>ココロ</t>
   </si>
   <si>
-    <t>康イエ（享年）</t>
-  </si>
-  <si>
     <t>ネプチューン</t>
   </si>
   <si>
@@ -177,12 +120,6 @@
     <t>ラオG</t>
   </si>
   <si>
-    <t>オニ丸</t>
-  </si>
-  <si>
-    <t>ビッグ・マム</t>
-  </si>
-  <si>
     <t>ガン・フォール</t>
   </si>
   <si>
@@ -192,15 +129,9 @@
     <t>スパンダイン</t>
   </si>
   <si>
-    <t>酋長（シャンディア）</t>
-  </si>
-  <si>
     <t>ベガパンク</t>
   </si>
   <si>
-    <t>ロキ</t>
-  </si>
-  <si>
     <t>ゴールドバーグ</t>
   </si>
   <si>
@@ -219,9 +150,6 @@
     <t>ジョーラ</t>
   </si>
   <si>
-    <t>リク・ドルド３世</t>
-  </si>
-  <si>
     <t>デン</t>
   </si>
   <si>
@@ -231,18 +159,6 @@
     <t>カイドウ</t>
   </si>
   <si>
-    <t>天狗山飛徹</t>
-  </si>
-  <si>
-    <t>黄猿</t>
-  </si>
-  <si>
-    <t>タイガー（享年）</t>
-  </si>
-  <si>
-    <t>おでん（享年）</t>
-  </si>
-  <si>
     <t>クイーン</t>
   </si>
   <si>
@@ -252,54 +168,24 @@
     <t>ブランニュー</t>
   </si>
   <si>
-    <t>お鶴（鶴女）</t>
-  </si>
-  <si>
-    <t>赤犬</t>
-  </si>
-  <si>
-    <t>ジャッジ</t>
-  </si>
-  <si>
     <t>アシュラ童子</t>
   </si>
   <si>
     <t>右大臣</t>
   </si>
   <si>
-    <t>トキ（享年）</t>
-  </si>
-  <si>
-    <t>ドラゴン</t>
-  </si>
-  <si>
-    <t>ニコ・オルビア（享年）</t>
-  </si>
-  <si>
     <t>パガヤ</t>
   </si>
   <si>
-    <t>藤虎</t>
-  </si>
-  <si>
-    <t>ダダン</t>
-  </si>
-  <si>
     <t>ロズワード聖</t>
   </si>
   <si>
     <t>モルガンズ</t>
   </si>
   <si>
-    <t>オロチ</t>
-  </si>
-  <si>
     <t>Tボーン</t>
   </si>
   <si>
-    <t>アンド（バスカビル）</t>
-  </si>
-  <si>
     <t>ラブーン</t>
   </si>
   <si>
@@ -309,9 +195,6 @@
     <t>マッハバイス</t>
   </si>
   <si>
-    <t>イワンコフ</t>
-  </si>
-  <si>
     <t>スクアード</t>
   </si>
   <si>
@@ -324,18 +207,9 @@
     <t>ベン・ベックマン</t>
   </si>
   <si>
-    <t>コブラ</t>
-  </si>
-  <si>
     <t>しのぶ</t>
   </si>
   <si>
-    <t>モリア</t>
-  </si>
-  <si>
-    <t>霜月牛マル（享年）</t>
-  </si>
-  <si>
     <t>トレーボル</t>
   </si>
   <si>
@@ -354,18 +228,12 @@
     <t>ゲンゾウ</t>
   </si>
   <si>
-    <t>バス（バスカビル）</t>
-  </si>
-  <si>
     <t>モモンガ</t>
   </si>
   <si>
     <t>ヒグマ</t>
   </si>
   <si>
-    <t>くま</t>
-  </si>
-  <si>
     <t>キング</t>
   </si>
   <si>
@@ -396,9 +264,6 @@
     <t>クロコダイル</t>
   </si>
   <si>
-    <t>ピンク</t>
-  </si>
-  <si>
     <t>タマゴ男爵</t>
   </si>
   <si>
@@ -408,18 +273,12 @@
     <t>風刃</t>
   </si>
   <si>
-    <t>雨月天ぷら（享年）</t>
-  </si>
-  <si>
     <t>マルコ</t>
   </si>
   <si>
     <t>トルコ</t>
   </si>
   <si>
-    <t>オトヒメ（享年）</t>
-  </si>
-  <si>
     <t>雷刃</t>
   </si>
   <si>
@@ -429,9 +288,6 @@
     <t>イゾウ</t>
   </si>
   <si>
-    <t>ネギ熊まりあ</t>
-  </si>
-  <si>
     <t>クリーク</t>
   </si>
   <si>
@@ -441,12 +297,6 @@
     <t>ディアマンテ</t>
   </si>
   <si>
-    <t>ミホーク</t>
-  </si>
-  <si>
-    <t>風月おむすび（享年）</t>
-  </si>
-  <si>
     <t>茶ひげ</t>
   </si>
   <si>
@@ -471,18 +321,6 @@
     <t>風影</t>
   </si>
   <si>
-    <t>ゲルニカ（享年）</t>
-  </si>
-  <si>
-    <t>C・ブリュレ</t>
-  </si>
-  <si>
-    <t>C・ヌストルテ</t>
-  </si>
-  <si>
-    <t>ベッジ</t>
-  </si>
-  <si>
     <t>半ぞう</t>
   </si>
   <si>
@@ -492,9 +330,6 @@
     <t>ジョズ</t>
   </si>
   <si>
-    <t>カビル（バスカビル）</t>
-  </si>
-  <si>
     <t>大黒</t>
   </si>
   <si>
@@ -504,9 +339,6 @@
     <t>ラフィット</t>
   </si>
   <si>
-    <t>ドフラミンゴ</t>
-  </si>
-  <si>
     <t>ヴェルゴ</t>
   </si>
   <si>
@@ -522,9 +354,6 @@
     <t>河松</t>
   </si>
   <si>
-    <t>黒ひげ</t>
-  </si>
-  <si>
     <t>ネコマムシ</t>
   </si>
   <si>
@@ -534,9 +363,6 @@
     <t>アイスバーグ</t>
   </si>
   <si>
-    <t>シーザー</t>
-  </si>
-  <si>
     <t>ピーカ</t>
   </si>
   <si>
@@ -546,12 +372,6 @@
     <t>スレイマン</t>
   </si>
   <si>
-    <t>トマトギャング</t>
-  </si>
-  <si>
-    <t>ベルメール（享年）</t>
-  </si>
-  <si>
     <t>シャンクス</t>
   </si>
   <si>
@@ -561,15 +381,9 @@
     <t>エネル</t>
   </si>
   <si>
-    <t>カン十郎</t>
-  </si>
-  <si>
     <t>ヒョウゾウ</t>
   </si>
   <si>
-    <t>ロシナンテ（コラソン）（享年）</t>
-  </si>
-  <si>
     <t>バスコ・ショット</t>
   </si>
   <si>
@@ -630,18 +444,9 @@
     <t>アブサロム</t>
   </si>
   <si>
-    <t>シンドリー（享年）</t>
-  </si>
-  <si>
-    <t>ミョスガルド聖</t>
-  </si>
-  <si>
     <t>ラッキー・ルウ</t>
   </si>
   <si>
-    <t>ウィーブル</t>
-  </si>
-  <si>
     <t>バンダー・デッケン九世</t>
   </si>
   <si>
@@ -666,9 +471,6 @@
     <t>タイルストン</t>
   </si>
   <si>
-    <t>スカーレット（享年）</t>
-  </si>
-  <si>
     <t>戦桃丸</t>
   </si>
   <si>
@@ -687,18 +489,12 @@
     <t>カルネ</t>
   </si>
   <si>
-    <t>ドレーク</t>
-  </si>
-  <si>
     <t>ゴッティ</t>
   </si>
   <si>
     <t>グラディウス</t>
   </si>
   <si>
-    <t>ルル</t>
-  </si>
-  <si>
     <t>シュラ</t>
   </si>
   <si>
@@ -720,15 +516,6 @@
     <t>チェス</t>
   </si>
   <si>
-    <t>ハンコック</t>
-  </si>
-  <si>
-    <t>アプー</t>
-  </si>
-  <si>
-    <t>ホーキンス</t>
-  </si>
-  <si>
     <t>マキノ</t>
   </si>
   <si>
@@ -738,21 +525,12 @@
     <t>ゲダツ</t>
   </si>
   <si>
-    <t>ロビン</t>
-  </si>
-  <si>
-    <t>ルッチ</t>
-  </si>
-  <si>
     <t>ジーザス・バージェス</t>
   </si>
   <si>
     <t>ブラックマリア</t>
   </si>
   <si>
-    <t>ホーディ</t>
-  </si>
-  <si>
     <t>フクロウ</t>
   </si>
   <si>
@@ -765,9 +543,6 @@
     <t>イナズマ</t>
   </si>
   <si>
-    <t>サンダーソニア</t>
-  </si>
-  <si>
     <t>シャーリー</t>
   </si>
   <si>
@@ -792,9 +567,6 @@
     <t>バッファロー</t>
   </si>
   <si>
-    <t>ニセそげキング</t>
-  </si>
-  <si>
     <t>クロマーリモ</t>
   </si>
   <si>
@@ -819,9 +591,6 @@
     <t>サイ</t>
   </si>
   <si>
-    <t>ペンギン</t>
-  </si>
-  <si>
     <t>コリブー</t>
   </si>
   <si>
@@ -858,9 +627,6 @@
     <t>フルボディ</t>
   </si>
   <si>
-    <t>マリーゴールド</t>
-  </si>
-  <si>
     <t>ワンダ</t>
   </si>
   <si>
@@ -870,9 +636,6 @@
     <t>ワンゼ</t>
   </si>
   <si>
-    <t>ロー</t>
-  </si>
-  <si>
     <t>ビシャ門</t>
   </si>
   <si>
@@ -891,12 +654,6 @@
     <t>カリファ</t>
   </si>
   <si>
-    <t>シャチ</t>
-  </si>
-  <si>
-    <t>ウィッカ</t>
-  </si>
-  <si>
     <t>知</t>
   </si>
   <si>
@@ -918,415 +675,718 @@
     <t>コトリ</t>
   </si>
   <si>
-    <t>日和</t>
+    <t>ジョニー</t>
+  </si>
+  <si>
+    <t>ロック</t>
+  </si>
+  <si>
+    <t>ペローナ</t>
+  </si>
+  <si>
+    <t>ゲンボウ</t>
+  </si>
+  <si>
+    <t>レオ</t>
+  </si>
+  <si>
+    <t>マンシェリー</t>
+  </si>
+  <si>
+    <t>ワダツミ</t>
+  </si>
+  <si>
+    <t>マシラ</t>
+  </si>
+  <si>
+    <t>デュバル</t>
+  </si>
+  <si>
+    <t>パール</t>
+  </si>
+  <si>
+    <t>スコッチ</t>
+  </si>
+  <si>
+    <t>マンジャロウ</t>
+  </si>
+  <si>
+    <t>悪</t>
+  </si>
+  <si>
+    <t>バルトロメオ</t>
+  </si>
+  <si>
+    <t>フカボシ</t>
+  </si>
+  <si>
+    <t>チャルロス聖</t>
+  </si>
+  <si>
+    <t>ブルーギリー</t>
+  </si>
+  <si>
+    <t>シープスヘッド</t>
+  </si>
+  <si>
+    <t>ワイパー</t>
+  </si>
+  <si>
+    <t>カマキリ</t>
+  </si>
+  <si>
+    <t>ブラハム</t>
+  </si>
+  <si>
+    <t>ドリップ</t>
+  </si>
+  <si>
+    <t>矢ざえもん</t>
+  </si>
+  <si>
+    <t>スピード</t>
+  </si>
+  <si>
+    <t>たしぎ</t>
+  </si>
+  <si>
+    <t>コアラ</t>
+  </si>
+  <si>
+    <t>リュウボシ</t>
+  </si>
+  <si>
+    <t>シャム</t>
+  </si>
+  <si>
+    <t>ブチ</t>
+  </si>
+  <si>
+    <t>サボ</t>
+  </si>
+  <si>
+    <t>ノジコ</t>
+  </si>
+  <si>
+    <t>うるティ</t>
+  </si>
+  <si>
+    <t>ベポ</t>
+  </si>
+  <si>
+    <t>イデオ</t>
+  </si>
+  <si>
+    <t>ヘルメッポ</t>
+  </si>
+  <si>
+    <t>キウイ</t>
+  </si>
+  <si>
+    <t>ラキ</t>
+  </si>
+  <si>
+    <t>コーザ</t>
+  </si>
+  <si>
+    <t>ネロ</t>
+  </si>
+  <si>
+    <t>シュガー</t>
+  </si>
+  <si>
+    <t>サンジ</t>
+  </si>
+  <si>
+    <t>モズ</t>
+  </si>
+  <si>
+    <t>コニス</t>
+  </si>
+  <si>
+    <t>地獄弁天</t>
+  </si>
+  <si>
+    <t>ナミ</t>
+  </si>
+  <si>
+    <t>ページワン</t>
+  </si>
+  <si>
+    <t>ステリー</t>
+  </si>
+  <si>
+    <t>マンボシ</t>
+  </si>
+  <si>
+    <t>ハットリ</t>
+  </si>
+  <si>
+    <t>カヤ</t>
+  </si>
+  <si>
+    <t>コビー</t>
+  </si>
+  <si>
+    <t>ケイミー</t>
+  </si>
+  <si>
+    <t>マーガレット</t>
+  </si>
+  <si>
+    <t>想</t>
+  </si>
+  <si>
+    <t>サルデス</t>
+  </si>
+  <si>
+    <t>シャルリア宮</t>
+  </si>
+  <si>
+    <t>マツゲ</t>
+  </si>
+  <si>
+    <t>ひばり</t>
+  </si>
+  <si>
+    <t>しらほし</t>
+  </si>
+  <si>
+    <t>暴</t>
+  </si>
+  <si>
+    <t>レベッカ</t>
+  </si>
+  <si>
+    <t>デリンジャー</t>
+  </si>
+  <si>
+    <t>カルー</t>
+  </si>
+  <si>
+    <t>イワンX</t>
+  </si>
+  <si>
+    <t>カウボーイ</t>
+  </si>
+  <si>
+    <t>モーム</t>
+  </si>
+  <si>
+    <t>キャロット</t>
+  </si>
+  <si>
+    <t>ストンプ</t>
+  </si>
+  <si>
+    <t>ケンタロウス</t>
+  </si>
+  <si>
+    <t>ヒコイチ</t>
+  </si>
+  <si>
+    <t>シュシュ</t>
+  </si>
+  <si>
+    <t>ちょめ</t>
+  </si>
+  <si>
+    <t>のらギツネ</t>
+  </si>
+  <si>
+    <t>にんじん</t>
+  </si>
+  <si>
+    <t>ピーマン</t>
+  </si>
+  <si>
+    <t>たまねぎ</t>
+  </si>
+  <si>
+    <t>アイサ</t>
+  </si>
+  <si>
+    <t>チムニー</t>
+  </si>
+  <si>
+    <t>モチャ</t>
+  </si>
+  <si>
+    <t>トコ</t>
+  </si>
+  <si>
+    <t>スマイリー</t>
+  </si>
+  <si>
+    <t>モンキー・D・ルフィ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンキー・D・ルフィ(7歳）</t>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロロノア・ゾロ</t>
+  </si>
+  <si>
+    <t>ウソップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トニートニー・チョッパー</t>
+  </si>
+  <si>
+    <t>ニコ・ロビン</t>
+  </si>
+  <si>
+    <t>ネフェルタリ・ビビ</t>
+  </si>
+  <si>
+    <t>ゴール・D・ロジャー</t>
+  </si>
+  <si>
+    <t>シャンクス（13歳）</t>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くいな</t>
+  </si>
+  <si>
+    <t>バギー（13歳）</t>
+    <rPh sb="6" eb="7">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モージ（リッチー搭乗時）</t>
+    <rPh sb="8" eb="10">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュラキュール・ミホーク</t>
+  </si>
+  <si>
+    <t>ベルメール</t>
+  </si>
+  <si>
+    <t>モンキー・D・ドラゴン</t>
+  </si>
+  <si>
+    <t>ジェム</t>
+  </si>
+  <si>
+    <t>ミキータ</t>
+  </si>
+  <si>
+    <t>ギャルディーノ</t>
+  </si>
+  <si>
+    <t>マリアンヌ</t>
+  </si>
+  <si>
+    <t>Dr.くれは</t>
+  </si>
+  <si>
+    <t>Dr.ヒルルク</t>
+  </si>
+  <si>
+    <t>ネフェルタリ・コブラ</t>
+  </si>
+  <si>
+    <t>ベンサム</t>
+  </si>
+  <si>
+    <t>ポートガス・D・エース(10歳）</t>
+    <rPh sb="14" eb="15">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポートガス・D・エース</t>
+  </si>
+  <si>
+    <t>ドロフィー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ベーブ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザラ </t>
+  </si>
+  <si>
+    <t>ダズ・ボーネス</t>
+  </si>
+  <si>
+    <t>バーボンJr.</t>
+  </si>
+  <si>
+    <t>つる</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ドフラミンゴ</t>
+  </si>
+  <si>
+    <t>バーソロミュー・くま</t>
+  </si>
+  <si>
+    <t>エドワード・ニューゲート</t>
+  </si>
+  <si>
+    <t>マーシャル・D・ティーチ</t>
+  </si>
+  <si>
+    <t>酋長</t>
+  </si>
+  <si>
+    <t>モンブラン・ノーランド</t>
+  </si>
+  <si>
+    <t>ロブ・ルッチ</t>
+  </si>
+  <si>
+    <t>ピープリ―・ルル</t>
+  </si>
+  <si>
+    <t>トム</t>
+  </si>
+  <si>
+    <t>バス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カビル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クローバー</t>
+  </si>
+  <si>
+    <t>ハグワール・D・サウロ</t>
+  </si>
+  <si>
+    <t>ニコ・オルビア</t>
+  </si>
+  <si>
+    <t>モンキー・D・ガープ</t>
+  </si>
+  <si>
+    <t>シンドリー</t>
+  </si>
+  <si>
+    <t>リューマ</t>
+  </si>
+  <si>
+    <t>シャーロット・ローラ</t>
+  </si>
+  <si>
+    <t>ジゴロウ</t>
+  </si>
+  <si>
+    <t>ゲッコー・モリア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーズ </t>
+  </si>
+  <si>
+    <t>カポネ・ベッジ</t>
+  </si>
+  <si>
+    <t>ジュエリー・ボニー(見た目）</t>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュエリー・ボニー</t>
+  </si>
+  <si>
+    <t>バジル・ホーキンス</t>
+  </si>
+  <si>
+    <t>ユースタス・キッド</t>
+  </si>
+  <si>
+    <t>スクラッチメン・アプー</t>
+  </si>
+  <si>
+    <t>X・ドレーク</t>
+  </si>
+  <si>
+    <t>トラファルガー・ロー</t>
+  </si>
+  <si>
+    <t>シルバーズ・レイリー</t>
+  </si>
+  <si>
+    <t>ボルサリーノ</t>
+  </si>
+  <si>
+    <t>ボア・ハンコック</t>
+  </si>
+  <si>
+    <t>ボア・サンダーソニア</t>
+  </si>
+  <si>
+    <t>ボア・マリーゴールド</t>
+  </si>
+  <si>
+    <t>サディちゃん</t>
+  </si>
+  <si>
+    <t>エンポリオ・イワンコフ</t>
+  </si>
+  <si>
+    <t>サカズキ</t>
+  </si>
+  <si>
+    <t>カーリー・ダダン</t>
+  </si>
+  <si>
+    <t>サボ（10歳）</t>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ショコラ</t>
+  </si>
+  <si>
+    <t>マウンブルテン</t>
+  </si>
+  <si>
+    <t>ホーディ・ジョーンズ</t>
+  </si>
+  <si>
+    <t>フィッシャー・タイガー</t>
+  </si>
+  <si>
+    <t>オトヒメ</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ミョスガルド聖</t>
+  </si>
+  <si>
+    <t>シーザー・クラウン</t>
+  </si>
+  <si>
+    <t>光月モモの助（未来の姿）</t>
+    <rPh sb="7" eb="9">
+      <t>ミライ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>光月モモの助</t>
+  </si>
+  <si>
+    <t>ベビー5</t>
+  </si>
+  <si>
+    <t>イッショウ</t>
+  </si>
+  <si>
+    <t>ゲルニカ</t>
+  </si>
+  <si>
+    <t>リク・ドルド3世</t>
+  </si>
+  <si>
+    <t>セニョール・ピンク</t>
+  </si>
+  <si>
+    <t>スカーレット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭カン十郎</t>
+  </si>
+  <si>
+    <t>ドンキホーテ・ロシナンテ</t>
+  </si>
+  <si>
+    <t>エドワード・ウィーブル</t>
+  </si>
+  <si>
+    <t>象主</t>
+  </si>
+  <si>
+    <t>雷ぞう</t>
+  </si>
+  <si>
+    <t>シャーロット・プリン</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ヨンジ</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・レイジュ</t>
+  </si>
+  <si>
+    <t>シャーロット・リンリン</t>
+  </si>
+  <si>
+    <t>シャーロット・プラリネ</t>
+  </si>
+  <si>
+    <t>シャーロット・ブリュレ</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ジャッジ</t>
+  </si>
+  <si>
+    <t>シャーロット・シフォン</t>
+  </si>
+  <si>
+    <t>シャーロット・ペロスペロー</t>
+  </si>
+  <si>
+    <t>シャーロット・クラッカー</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・イチジ</t>
+  </si>
+  <si>
+    <t>ヴィンスモーク・ニジ</t>
+  </si>
+  <si>
+    <t>ステューシー</t>
+  </si>
+  <si>
+    <t>シャーロット・モンドール</t>
+  </si>
+  <si>
+    <t>シャーロット・スムージー</t>
+  </si>
+  <si>
+    <t>シャーロット・カタクリ</t>
+  </si>
+  <si>
+    <t>シャーロット・ダイフク</t>
+  </si>
+  <si>
+    <t>シャーロット・オーブン</t>
+  </si>
+  <si>
+    <t>ヨルル</t>
+  </si>
+  <si>
+    <t>シャーロット・フランペ</t>
+  </si>
+  <si>
+    <t>ベロ・ベティ</t>
+  </si>
+  <si>
+    <t>お玉</t>
+  </si>
+  <si>
+    <t>光月スキヤキ</t>
+  </si>
+  <si>
+    <t>お鶴</t>
+  </si>
+  <si>
+    <t>菊之丞</t>
+  </si>
+  <si>
+    <t>光月日和</t>
+  </si>
+  <si>
+    <t>霜月康イエ</t>
+  </si>
+  <si>
+    <t>黒炭オロチ</t>
+  </si>
+  <si>
+    <t>オニ丸 (牛鬼丸)</t>
+  </si>
+  <si>
+    <t>霜月牛マル</t>
+  </si>
+  <si>
+    <t>霜月コウ三郎</t>
+  </si>
+  <si>
+    <t>光月おでん</t>
+  </si>
+  <si>
+    <t>光月トキ</t>
+  </si>
+  <si>
+    <t>黒炭ひぐらし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸（胡坐時）</t>
+    <rPh sb="6" eb="9">
+      <t>アグラジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八茶</t>
+  </si>
+  <si>
+    <t>雨月天ぷら</t>
+  </si>
+  <si>
+    <t>風月おむすび</t>
+  </si>
+  <si>
+    <t>S-スネーク</t>
+  </si>
+  <si>
+    <t>S-ホーク</t>
+  </si>
+  <si>
+    <t>S-ベア</t>
+  </si>
+  <si>
+    <t>S-シャーク</t>
+  </si>
+  <si>
+    <t>欲</t>
   </si>
   <si>
     <t>孔雀</t>
-  </si>
-  <si>
-    <t>ジョニー</t>
-  </si>
-  <si>
-    <t>ロック</t>
-  </si>
-  <si>
-    <t>ニセナミ</t>
-  </si>
-  <si>
-    <t>ペローナ</t>
-  </si>
-  <si>
-    <t>ゲンボウ</t>
-  </si>
-  <si>
-    <t>レオ</t>
-  </si>
-  <si>
-    <t>マンシェリー</t>
-  </si>
-  <si>
-    <t>ボニー</t>
-  </si>
-  <si>
-    <t>ワダツミ</t>
-  </si>
-  <si>
-    <t>マシラ</t>
-  </si>
-  <si>
-    <t>デュバル</t>
-  </si>
-  <si>
-    <t>パール</t>
-  </si>
-  <si>
-    <t>レイジュ</t>
-  </si>
-  <si>
-    <t>スコッチ</t>
-  </si>
-  <si>
-    <t>マンジャロウ</t>
-  </si>
-  <si>
-    <t>悪</t>
-  </si>
-  <si>
-    <t>バルトロメオ</t>
-  </si>
-  <si>
-    <t>ベビー５</t>
-  </si>
-  <si>
-    <t>フカボシ</t>
-  </si>
-  <si>
-    <t>チャルロス聖</t>
-  </si>
-  <si>
-    <t>ブルーギリー</t>
-  </si>
-  <si>
-    <t>シープスヘッド</t>
-  </si>
-  <si>
-    <t>ワイパー</t>
-  </si>
-  <si>
-    <t>カマキリ</t>
-  </si>
-  <si>
-    <t>ブラハム</t>
-  </si>
-  <si>
-    <t>ドリップ</t>
-  </si>
-  <si>
-    <t>矢ざえもん</t>
-  </si>
-  <si>
-    <t>スピード</t>
-  </si>
-  <si>
-    <t>キッド</t>
-  </si>
-  <si>
-    <t>たしぎ</t>
-  </si>
-  <si>
-    <t>コアラ</t>
-  </si>
-  <si>
-    <t>リュウボシ</t>
-  </si>
-  <si>
-    <t>サディ</t>
-  </si>
-  <si>
-    <t>シャム</t>
-  </si>
-  <si>
-    <t>ブチ</t>
-  </si>
-  <si>
-    <t>くいな（享年）</t>
-  </si>
-  <si>
-    <t>サボ</t>
-  </si>
-  <si>
-    <t>ノジコ</t>
-  </si>
-  <si>
-    <t>うるティ</t>
-  </si>
-  <si>
-    <t>ベポ</t>
-  </si>
-  <si>
-    <t>イデオ</t>
-  </si>
-  <si>
-    <t>ヘルメッポ</t>
-  </si>
-  <si>
-    <t>キウイ</t>
-  </si>
-  <si>
-    <t>ラキ</t>
-  </si>
-  <si>
-    <t>コーザ</t>
-  </si>
-  <si>
-    <t>ネロ</t>
-  </si>
-  <si>
-    <t>シュガー</t>
-  </si>
-  <si>
-    <t>菊の丞</t>
-  </si>
-  <si>
-    <t>エース（享年）</t>
-  </si>
-  <si>
-    <t>ゾロ</t>
-  </si>
-  <si>
-    <t>サンジ</t>
-  </si>
-  <si>
-    <t>イチジ</t>
-  </si>
-  <si>
-    <t>ニジ</t>
-  </si>
-  <si>
-    <t>ヨンジ</t>
-  </si>
-  <si>
-    <t>モズ</t>
-  </si>
-  <si>
-    <t>コニス</t>
-  </si>
-  <si>
-    <t>地獄弁天</t>
-  </si>
-  <si>
-    <t>ナミ</t>
-  </si>
-  <si>
-    <t>ページワン</t>
-  </si>
-  <si>
-    <t>ステリー</t>
-  </si>
-  <si>
-    <t>マンボシ</t>
-  </si>
-  <si>
-    <t>キュイーン</t>
-  </si>
-  <si>
-    <t>ハットリ</t>
-  </si>
-  <si>
-    <t>ルフィ</t>
-  </si>
-  <si>
-    <t>ウソップ</t>
-  </si>
-  <si>
-    <t>カヤ</t>
-  </si>
-  <si>
-    <t>ビビ</t>
-  </si>
-  <si>
-    <t>コビー</t>
-  </si>
-  <si>
-    <t>ケイミー</t>
-  </si>
-  <si>
-    <t>マーガレット</t>
-  </si>
-  <si>
-    <t>想</t>
-  </si>
-  <si>
-    <t>サルデス</t>
-  </si>
-  <si>
-    <t>チョッパー</t>
-  </si>
-  <si>
-    <t>シャルリア宮</t>
-  </si>
-  <si>
-    <t>マツゲ</t>
-  </si>
-  <si>
-    <t>ひばり</t>
-  </si>
-  <si>
-    <t>しらほし</t>
-  </si>
-  <si>
-    <t>暴</t>
-  </si>
-  <si>
-    <t>レベッカ</t>
-  </si>
-  <si>
-    <t>デリンジャー</t>
-  </si>
-  <si>
-    <t>カルー</t>
-  </si>
-  <si>
-    <t>イワンX</t>
-  </si>
-  <si>
-    <t>カウボーイ</t>
-  </si>
-  <si>
-    <t>モーム</t>
-  </si>
-  <si>
-    <t>キャロット</t>
-  </si>
-  <si>
-    <t>ストンプ</t>
-  </si>
-  <si>
-    <t>ケンタロウス</t>
-  </si>
-  <si>
-    <t>マイケル</t>
-  </si>
-  <si>
-    <t>ホイケル</t>
-  </si>
-  <si>
-    <t>ヒコイチ</t>
-  </si>
-  <si>
-    <t>バーボンＪｒ.</t>
-  </si>
-  <si>
-    <t>シュシュ</t>
-  </si>
-  <si>
-    <t>ちょめ</t>
-  </si>
-  <si>
-    <t>のらギツネ</t>
-  </si>
-  <si>
-    <t>にんじん</t>
-  </si>
-  <si>
-    <t>ピーマン</t>
-  </si>
-  <si>
-    <t>たまねぎ</t>
-  </si>
-  <si>
-    <t>アイサ</t>
-  </si>
-  <si>
-    <t>チムニー</t>
-  </si>
-  <si>
-    <t>モチャ</t>
-  </si>
-  <si>
-    <t>モモの助</t>
-  </si>
-  <si>
-    <t>セラフィム</t>
-  </si>
-  <si>
-    <t>玉</t>
-  </si>
-  <si>
-    <t>トコ</t>
-  </si>
-  <si>
-    <t>スマイリー</t>
-  </si>
-  <si>
-    <t>ペッツ</t>
-  </si>
-  <si>
-    <t>ジニー（享年）</t>
+    <rPh sb="0" eb="2">
+      <t>クジャク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アナナ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プリン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フランペ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マリアンヌ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ローラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プラリネ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジェム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダズ・ボーネス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベンサム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミキータ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ギャルディーノ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モンドール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クラッカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オペラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アマンド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カタクリ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ペロスペロー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒルルク（享年）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベーブ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドロフィー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ザラ</t>
+    <t>ジニー</t>
+  </si>
+  <si>
+    <t>ロックス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1392,6 +1452,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1691,39 +1755,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9260E853-4111-4EA2-B584-BE6956775AD1}">
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="29.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>401</v>
+        <v>293</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>400</v>
+        <v>292</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>399</v>
+        <v>295</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -1731,7 +1795,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -1739,7 +1803,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -1747,7 +1811,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -1755,55 +1819,55 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>393</v>
+        <v>303</v>
       </c>
       <c r="B14">
         <v>11</v>
@@ -1811,135 +1875,135 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>389</v>
+        <v>286</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>383</v>
+        <v>287</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>385</v>
+        <v>289</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>388</v>
+        <v>304</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>372</v>
+        <v>284</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>374</v>
+        <v>281</v>
       </c>
       <c r="B28">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>404</v>
+        <v>279</v>
       </c>
       <c r="B29">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>376</v>
+        <v>278</v>
       </c>
       <c r="B31">
         <v>16</v>
@@ -1947,7 +2011,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>275</v>
       </c>
       <c r="B32">
         <v>16</v>
@@ -1955,7 +2019,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="B33">
         <v>16</v>
@@ -1963,7 +2027,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>379</v>
+        <v>277</v>
       </c>
       <c r="B34">
         <v>16</v>
@@ -1971,87 +2035,87 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>368</v>
+        <v>271</v>
       </c>
       <c r="B35">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>369</v>
+        <v>273</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>370</v>
+        <v>274</v>
       </c>
       <c r="B37">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B38">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>362</v>
+        <v>272</v>
       </c>
       <c r="B39">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="B40">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="B41">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>406</v>
+        <v>269</v>
       </c>
       <c r="B42">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>365</v>
+        <v>268</v>
       </c>
       <c r="B43">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>366</v>
+        <v>270</v>
       </c>
       <c r="B44">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="B45">
         <v>18</v>
@@ -2059,79 +2123,79 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="B46">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="B47">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>361</v>
+        <v>264</v>
       </c>
       <c r="B48">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>344</v>
+        <v>265</v>
       </c>
       <c r="B49">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>353</v>
+        <v>267</v>
       </c>
       <c r="B50">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="B51">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="B52">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>357</v>
+        <v>262</v>
       </c>
       <c r="B54">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="B55">
         <v>20</v>
@@ -2139,47 +2203,47 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="B56">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>346</v>
+        <v>261</v>
       </c>
       <c r="B57">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>347</v>
+        <v>259</v>
       </c>
       <c r="B58">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>348</v>
+        <v>260</v>
       </c>
       <c r="B59">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="B60">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>350</v>
+        <v>296</v>
       </c>
       <c r="B61">
         <v>21</v>
@@ -2187,7 +2251,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="B62">
         <v>21</v>
@@ -2195,7 +2259,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>352</v>
+        <v>255</v>
       </c>
       <c r="B63">
         <v>21</v>
@@ -2203,47 +2267,47 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>332</v>
+        <v>254</v>
       </c>
       <c r="B64">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>333</v>
+        <v>386</v>
       </c>
       <c r="B65">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="B66">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="B67">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>336</v>
+        <v>256</v>
       </c>
       <c r="B68">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>337</v>
+        <v>247</v>
       </c>
       <c r="B69">
         <v>22</v>
@@ -2251,7 +2315,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="B70">
         <v>22</v>
@@ -2259,7 +2323,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="B71">
         <v>22</v>
@@ -2267,7 +2331,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>340</v>
+        <v>249</v>
       </c>
       <c r="B72">
         <v>22</v>
@@ -2275,7 +2339,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>341</v>
+        <v>248</v>
       </c>
       <c r="B73">
         <v>22</v>
@@ -2283,7 +2347,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>342</v>
+        <v>251</v>
       </c>
       <c r="B74">
         <v>22</v>
@@ -2291,7 +2355,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="B75">
         <v>22</v>
@@ -2299,47 +2363,47 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="B76">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="B77">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="B78">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>327</v>
+        <v>409</v>
       </c>
       <c r="B79">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>328</v>
+        <v>244</v>
       </c>
       <c r="B80">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>329</v>
+        <v>240</v>
       </c>
       <c r="B81">
         <v>23</v>
@@ -2347,7 +2411,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="B82">
         <v>23</v>
@@ -2355,47 +2419,47 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>412</v>
+        <v>237</v>
       </c>
       <c r="B83">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="B84">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="B86">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="B87">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B88">
         <v>24</v>
@@ -2403,7 +2467,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="B89">
         <v>24</v>
@@ -2411,7 +2475,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="B90">
         <v>24</v>
@@ -2419,7 +2483,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="B91">
         <v>24</v>
@@ -2427,7 +2491,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="B92">
         <v>24</v>
@@ -2435,7 +2499,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B93">
         <v>24</v>
@@ -2443,7 +2507,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="B94">
         <v>24</v>
@@ -2451,7 +2515,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="B95">
         <v>24</v>
@@ -2459,7 +2523,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>321</v>
+        <v>227</v>
       </c>
       <c r="B96">
         <v>24</v>
@@ -2467,7 +2531,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="B97">
         <v>24</v>
@@ -2475,7 +2539,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>323</v>
+        <v>226</v>
       </c>
       <c r="B98">
         <v>24</v>
@@ -2483,7 +2547,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="B99">
         <v>24</v>
@@ -2491,47 +2555,47 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B100">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>291</v>
+        <v>387</v>
       </c>
       <c r="B101">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="B102">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="B103">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="B105">
         <v>25</v>
@@ -2539,7 +2603,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="B106">
         <v>25</v>
@@ -2547,7 +2611,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="B107">
         <v>25</v>
@@ -2555,7 +2619,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>304</v>
+        <v>216</v>
       </c>
       <c r="B108">
         <v>25</v>
@@ -2563,7 +2627,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>305</v>
+        <v>210</v>
       </c>
       <c r="B109">
         <v>25</v>
@@ -2571,7 +2635,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="B110">
         <v>25</v>
@@ -2579,7 +2643,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>307</v>
+        <v>221</v>
       </c>
       <c r="B111">
         <v>25</v>
@@ -2587,7 +2651,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>309</v>
+        <v>124</v>
       </c>
       <c r="B112">
         <v>25</v>
@@ -2595,7 +2659,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="B113">
         <v>25</v>
@@ -2603,55 +2667,55 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="B114">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="B115">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="B116">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="B117">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B118">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="B119">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="B120">
         <v>26</v>
@@ -2659,7 +2723,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B121">
         <v>26</v>
@@ -2667,7 +2731,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>295</v>
+        <v>207</v>
       </c>
       <c r="B122">
         <v>26</v>
@@ -2675,7 +2739,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>407</v>
+        <v>343</v>
       </c>
       <c r="B123">
         <v>26</v>
@@ -2683,7 +2747,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="B124">
         <v>26</v>
@@ -2691,63 +2755,63 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="B125">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>264</v>
+        <v>201</v>
       </c>
       <c r="B126">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>266</v>
+        <v>381</v>
       </c>
       <c r="B127">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>269</v>
+        <v>392</v>
       </c>
       <c r="B128">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>410</v>
       </c>
       <c r="B129">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="B130">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="B131">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="B132">
         <v>27</v>
@@ -2755,7 +2819,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="B133">
         <v>27</v>
@@ -2763,7 +2827,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>283</v>
+        <v>189</v>
       </c>
       <c r="B134">
         <v>27</v>
@@ -2771,7 +2835,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="B135">
         <v>27</v>
@@ -2779,7 +2843,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="B136">
         <v>27</v>
@@ -2787,7 +2851,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>286</v>
+        <v>186</v>
       </c>
       <c r="B137">
         <v>27</v>
@@ -2795,7 +2859,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="B138">
         <v>27</v>
@@ -2803,7 +2867,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="B139">
         <v>27</v>
@@ -2811,7 +2875,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="B140">
         <v>27</v>
@@ -2819,47 +2883,47 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="B141">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="B142">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="B143">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="B144">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>423</v>
+        <v>204</v>
       </c>
       <c r="B145">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="B146">
         <v>28</v>
@@ -2867,7 +2931,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="B147">
         <v>28</v>
@@ -2875,7 +2939,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="B148">
         <v>28</v>
@@ -2883,7 +2947,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="B149">
         <v>28</v>
@@ -2891,7 +2955,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="B150">
         <v>28</v>
@@ -2899,7 +2963,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>279</v>
+        <v>372</v>
       </c>
       <c r="B151">
         <v>28</v>
@@ -2907,47 +2971,47 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="B152">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="B153">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="B154">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="B155">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="B156">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="B157">
         <v>29</v>
@@ -2955,7 +3019,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="B158">
         <v>29</v>
@@ -2963,7 +3027,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="B159">
         <v>29</v>
@@ -2971,7 +3035,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="B160">
         <v>29</v>
@@ -2979,7 +3043,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="B161">
         <v>29</v>
@@ -2987,7 +3051,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="B162">
         <v>29</v>
@@ -2995,7 +3059,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>265</v>
+        <v>190</v>
       </c>
       <c r="B163">
         <v>29</v>
@@ -3003,7 +3067,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="B164">
         <v>29</v>
@@ -3011,7 +3075,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="B165">
         <v>29</v>
@@ -3019,55 +3083,55 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B166">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="B167">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="B168">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="B169">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="B170">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>421</v>
+        <v>180</v>
       </c>
       <c r="B171">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="B172">
         <v>30</v>
@@ -3075,7 +3139,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="B173">
         <v>30</v>
@@ -3083,7 +3147,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="B174">
         <v>30</v>
@@ -3091,7 +3155,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="B175">
         <v>30</v>
@@ -3099,7 +3163,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="B176">
         <v>30</v>
@@ -3107,7 +3171,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>249</v>
+        <v>358</v>
       </c>
       <c r="B177">
         <v>30</v>
@@ -3115,7 +3179,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>251</v>
+        <v>366</v>
       </c>
       <c r="B178">
         <v>30</v>
@@ -3123,7 +3187,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>252</v>
+        <v>367</v>
       </c>
       <c r="B179">
         <v>30</v>
@@ -3131,7 +3195,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="B180">
         <v>30</v>
@@ -3139,7 +3203,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="B181">
         <v>30</v>
@@ -3147,7 +3211,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="B182">
         <v>30</v>
@@ -3155,55 +3219,55 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="B183">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="B184">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="B185">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>410</v>
+        <v>178</v>
       </c>
       <c r="B186">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="B187">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>233</v>
+        <v>170</v>
       </c>
       <c r="B188">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="B189">
         <v>31</v>
@@ -3211,95 +3275,95 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="B190">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="B191">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="B192">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>226</v>
+        <v>350</v>
       </c>
       <c r="B193">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>227</v>
+        <v>352</v>
       </c>
       <c r="B194">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="B195">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="B196">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>218</v>
+        <v>316</v>
       </c>
       <c r="B197">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="B198">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="B199">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="B200">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="B201">
         <v>33</v>
@@ -3307,7 +3371,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="B202">
         <v>33</v>
@@ -3315,55 +3379,55 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>175</v>
+        <v>339</v>
       </c>
       <c r="B203">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B204">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="B205">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="B206">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="B207">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>215</v>
+        <v>151</v>
       </c>
       <c r="B208">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="B209">
         <v>34</v>
@@ -3371,63 +3435,63 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B210">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="B211">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="B212">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>202</v>
+        <v>380</v>
       </c>
       <c r="B213">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="B214">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B215">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="B216">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="B217">
         <v>35</v>
@@ -3435,7 +3499,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="B218">
         <v>35</v>
@@ -3443,7 +3507,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="B219">
         <v>35</v>
@@ -3451,7 +3515,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="B220">
         <v>35</v>
@@ -3459,79 +3523,79 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B221">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B222">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="B223">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="B224">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B225">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="B226">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>192</v>
+        <v>382</v>
       </c>
       <c r="B227">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>193</v>
+        <v>384</v>
       </c>
       <c r="B228">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>194</v>
+        <v>399</v>
       </c>
       <c r="B229">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="B230">
         <v>36</v>
@@ -3539,7 +3603,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="B231">
         <v>36</v>
@@ -3547,367 +3611,367 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="B232">
         <v>36</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>413</v>
+        <v>131</v>
       </c>
       <c r="B233">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="B234">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="B235">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="B236">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>178</v>
+        <v>369</v>
       </c>
       <c r="B237">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="B238">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="B239">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>414</v>
+        <v>130</v>
       </c>
       <c r="B240">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>181</v>
+        <v>397</v>
       </c>
       <c r="B241">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>182</v>
+        <v>417</v>
       </c>
       <c r="B242">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>183</v>
+        <v>311</v>
       </c>
       <c r="B243">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="B244">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="B245">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="B246">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="B247">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="B248">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="B249">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="B250">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="B251">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B252">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="B253">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="B254">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="B255">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="B256">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="B257">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>168</v>
+        <v>330</v>
       </c>
       <c r="B258">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="B259">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="B260">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>154</v>
+        <v>430</v>
       </c>
       <c r="B261">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="B262">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>156</v>
+        <v>328</v>
       </c>
       <c r="B263">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="B264">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="B265">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="B266">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="B267">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="B268">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="B269">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="B270">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>147</v>
+        <v>325</v>
       </c>
       <c r="B271">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="B272">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B273">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="B274">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="B275">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="B276">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>153</v>
+        <v>336</v>
       </c>
       <c r="B277">
         <v>42</v>
@@ -3915,151 +3979,151 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="B278">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>138</v>
+        <v>347</v>
       </c>
       <c r="B279">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="B280">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="B281">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="B282">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>133</v>
+        <v>376</v>
       </c>
       <c r="B283">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="B284">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="B285">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>136</v>
+        <v>306</v>
       </c>
       <c r="B286">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B287">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>125</v>
+        <v>390</v>
       </c>
       <c r="B288">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>415</v>
+        <v>94</v>
       </c>
       <c r="B289">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>126</v>
+        <v>431</v>
       </c>
       <c r="B290">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B291">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B292">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="B293">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="B294">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>134</v>
+        <v>423</v>
       </c>
       <c r="B295">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="B296">
         <v>45</v>
@@ -4067,7 +4131,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="B297">
         <v>45</v>
@@ -4075,7 +4139,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="B298">
         <v>45</v>
@@ -4083,7 +4147,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="B299">
         <v>45</v>
@@ -4091,127 +4155,127 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B300">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="B301">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B302">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>119</v>
+        <v>394</v>
       </c>
       <c r="B303">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B304">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="B305">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="B306">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="B307">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B308">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B309">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B310">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B311">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="B312">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="B313">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>417</v>
+        <v>378</v>
       </c>
       <c r="B314">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="B315">
         <v>47</v>
@@ -4219,7 +4283,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>117</v>
+        <v>326</v>
       </c>
       <c r="B316">
         <v>47</v>
@@ -4227,7 +4291,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="B317">
         <v>47</v>
@@ -4235,863 +4299,927 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>67</v>
+        <v>342</v>
       </c>
       <c r="B318">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="B319">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>418</v>
+        <v>69</v>
       </c>
       <c r="B320">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="B321">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B322">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="B323">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B324">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B325">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>104</v>
+        <v>334</v>
       </c>
       <c r="B326">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B327">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="B328">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B329">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
-        <v>98</v>
+        <v>400</v>
       </c>
       <c r="B330">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>101</v>
+        <v>401</v>
       </c>
       <c r="B331">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>99</v>
+        <v>402</v>
       </c>
       <c r="B332">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B333">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B334">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>422</v>
+        <v>57</v>
       </c>
       <c r="B335">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="B336">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="B337">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>31</v>
+        <v>315</v>
       </c>
       <c r="B338">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="B339">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="B340">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>87</v>
+        <v>414</v>
       </c>
       <c r="B341">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="B342">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B343">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B344">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B345">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="B346">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
-        <v>89</v>
+        <v>301</v>
       </c>
       <c r="B347">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="B348">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B349">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="B350">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="B351">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B352">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B353">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
-        <v>166</v>
+        <v>375</v>
       </c>
       <c r="B354">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>69</v>
+        <v>412</v>
       </c>
       <c r="B355">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
-        <v>71</v>
+        <v>308</v>
       </c>
       <c r="B356">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="B357">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
-        <v>75</v>
+        <v>362</v>
       </c>
       <c r="B358">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>70</v>
+        <v>363</v>
       </c>
       <c r="B359">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B360">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>64</v>
+        <v>371</v>
       </c>
       <c r="B361">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
-        <v>61</v>
+        <v>408</v>
       </c>
       <c r="B362">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B363">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>60</v>
+        <v>391</v>
       </c>
       <c r="B364">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B365">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B366">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B367">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
-        <v>55</v>
+        <v>356</v>
       </c>
       <c r="B368">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>56</v>
+        <v>344</v>
       </c>
       <c r="B369">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
+        <v>40</v>
+      </c>
+      <c r="B370">
         <v>59</v>
-      </c>
-      <c r="B370">
-        <v>63</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>57</v>
+        <v>377</v>
       </c>
       <c r="B371">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B372">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B373">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B374">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B375">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B376">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
-        <v>420</v>
+        <v>36</v>
       </c>
       <c r="B377">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B378">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B379">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>23</v>
+        <v>329</v>
       </c>
       <c r="B380">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B381">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B382">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B383">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
-        <v>46</v>
+        <v>333</v>
       </c>
       <c r="B384">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>43</v>
+        <v>314</v>
       </c>
       <c r="B385">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B386">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
-        <v>41</v>
+        <v>388</v>
       </c>
       <c r="B387">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>42</v>
+        <v>415</v>
       </c>
       <c r="B388">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
-        <v>40</v>
+        <v>413</v>
       </c>
       <c r="B389">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B390">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B391">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B392">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
-        <v>33</v>
+        <v>411</v>
       </c>
       <c r="B393">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
-        <v>34</v>
+        <v>327</v>
       </c>
       <c r="B394">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B395">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B396">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B397">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B398">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B399">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c r="B400">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B401">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B402">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
-        <v>25</v>
+        <v>340</v>
       </c>
       <c r="B403">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
-        <v>65</v>
+        <v>355</v>
       </c>
       <c r="B404">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B405">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B406">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B407">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B408">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B409">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B410">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="B411">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
-        <v>18</v>
+        <v>419</v>
       </c>
       <c r="B412">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
-        <v>14</v>
+        <v>420</v>
       </c>
       <c r="B413">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
-        <v>13</v>
+        <v>337</v>
       </c>
       <c r="B414">
-        <v>120</v>
+        <v>85</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
-        <v>12</v>
+        <v>418</v>
       </c>
       <c r="B415">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B416">
-        <v>153</v>
+        <v>90</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B417">
-        <v>156</v>
+        <v>92</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B418">
-        <v>159</v>
+        <v>97</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B419">
-        <v>160</v>
+        <v>99</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B420">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
-        <v>8</v>
+        <v>338</v>
       </c>
       <c r="B421">
-        <v>160</v>
+        <v>127</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="B422">
-        <v>344</v>
+        <v>141</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B423">
-        <v>408</v>
+        <v>153</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B424">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A425" t="s">
+        <v>346</v>
+      </c>
+      <c r="B425">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A426" t="s">
+        <v>3</v>
+      </c>
+      <c r="B426">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A427" t="s">
+        <v>4</v>
+      </c>
+      <c r="B427">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A428" t="s">
+        <v>2</v>
+      </c>
+      <c r="B428">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A429" t="s">
+        <v>421</v>
+      </c>
+      <c r="B429">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A430" t="s">
+        <v>403</v>
+      </c>
+      <c r="B430">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A431" t="s">
+        <v>1</v>
+      </c>
+      <c r="B431">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A432" t="s">
+        <v>383</v>
+      </c>
+      <c r="B432">
         <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B424">
-    <sortCondition ref="B401:B424"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B432">
+    <sortCondition ref="B1:B432"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
